--- a/results/AutoEIT_Scored_38006-2A.xlsx
+++ b/results/AutoEIT_Scored_38006-2A.xlsx
@@ -565,7 +565,7 @@
         <v>0.8</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.707</v>
+        <v>0.534</v>
       </c>
     </row>
     <row r="3">
@@ -597,7 +597,7 @@
         <v>1</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.748</v>
+        <v>0.551</v>
       </c>
     </row>
     <row r="4">
@@ -629,7 +629,7 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.575</v>
+        <v>0.489</v>
       </c>
     </row>
     <row r="5">
@@ -661,7 +661,7 @@
         <v>0.8</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.694</v>
+        <v>0.529</v>
       </c>
     </row>
     <row r="6">
@@ -693,7 +693,7 @@
         <v>0.25</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.575</v>
+        <v>0.489</v>
       </c>
     </row>
     <row r="7">
@@ -725,7 +725,7 @@
         <v>0.667</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.655</v>
+        <v>0.515</v>
       </c>
     </row>
     <row r="8">
@@ -757,7 +757,7 @@
         <v>0.333</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.575</v>
+        <v>0.489</v>
       </c>
     </row>
     <row r="9">
@@ -789,7 +789,7 @@
         <v>0.571</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0.633</v>
+        <v>0.506</v>
       </c>
     </row>
     <row r="10">
@@ -821,7 +821,7 @@
         <v>0.429</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.581</v>
+        <v>0.489</v>
       </c>
     </row>
     <row r="11">
@@ -853,7 +853,7 @@
         <v>0.714</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>0.675</v>
+        <v>0.522</v>
       </c>
     </row>
     <row r="12">
@@ -885,7 +885,7 @@
         <v>0.625</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>0.651</v>
+        <v>0.512</v>
       </c>
     </row>
     <row r="13">
@@ -917,7 +917,7 @@
         <v>0.667</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.666</v>
+        <v>0.518</v>
       </c>
     </row>
     <row r="14">
@@ -949,7 +949,7 @@
         <v>0.5</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.599</v>
+        <v>0.497</v>
       </c>
     </row>
     <row r="15">
@@ -981,7 +981,7 @@
         <v>0.625</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>0.655</v>
+        <v>0.514</v>
       </c>
     </row>
     <row r="16">
@@ -1013,7 +1013,7 @@
         <v>0.375</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>0.575</v>
+        <v>0.489</v>
       </c>
     </row>
     <row r="17">
@@ -1045,7 +1045,7 @@
         <v>0.222</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>0.575</v>
+        <v>0.489</v>
       </c>
     </row>
     <row r="18">
@@ -1077,7 +1077,7 @@
         <v>0.444</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>0.604</v>
+        <v>0.498</v>
       </c>
     </row>
     <row r="19">
@@ -1109,7 +1109,7 @@
         <v>0.429</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>0.586</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="20">
@@ -1141,7 +1141,7 @@
         <v>0.333</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>0.575</v>
+        <v>0.489</v>
       </c>
     </row>
     <row r="21">
@@ -1173,7 +1173,7 @@
         <v>0.636</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>0.649</v>
+        <v>0.511</v>
       </c>
     </row>
     <row r="22">
@@ -1205,7 +1205,7 @@
         <v>0.545</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>0.617</v>
+        <v>0.502</v>
       </c>
     </row>
     <row r="23">
@@ -1237,7 +1237,7 @@
         <v>0.444</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>0.604</v>
+        <v>0.497</v>
       </c>
     </row>
     <row r="24">
@@ -1269,7 +1269,7 @@
         <v>0.3</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>0.575</v>
+        <v>0.489</v>
       </c>
     </row>
     <row r="25">
@@ -1301,7 +1301,7 @@
         <v>0.125</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>0.575</v>
+        <v>0.489</v>
       </c>
     </row>
     <row r="26">
@@ -1333,7 +1333,7 @@
         <v>0.6</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>0.64</v>
+        <v>0.508</v>
       </c>
     </row>
     <row r="27">
@@ -1365,7 +1365,7 @@
         <v>0.222</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>0.575</v>
+        <v>0.489</v>
       </c>
     </row>
     <row r="28">
@@ -1397,7 +1397,7 @@
         <v>0.364</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>0.575</v>
+        <v>0.489</v>
       </c>
     </row>
     <row r="29">
@@ -1429,7 +1429,7 @@
         <v>0.4</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>0.595</v>
+        <v>0.495</v>
       </c>
     </row>
     <row r="30">
@@ -1461,7 +1461,7 @@
         <v>0.5</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>0.62</v>
+        <v>0.503</v>
       </c>
     </row>
     <row r="31">
@@ -1493,7 +1493,7 @@
         <v>0.273</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>0.575</v>
+        <v>0.489</v>
       </c>
     </row>
     <row r="32">
